--- a/demo2.xlsx
+++ b/demo2.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="26805" windowHeight="12975"/>
+    <workbookView windowWidth="27015" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="47">
   <si>
     <t>LoginSales</t>
   </si>
@@ -41,6 +42,42 @@
     <t>Destination</t>
   </si>
   <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Is End User</t>
+  </si>
+  <si>
+    <t>Sell From</t>
+  </si>
+  <si>
+    <t>Yard Address</t>
+  </si>
+  <si>
+    <t>Anson Ni</t>
+  </si>
+  <si>
+    <t>DDP</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>Edmonton</t>
+  </si>
+  <si>
+    <t>Precise Pipe</t>
+  </si>
+  <si>
+    <t>Precise Pipe Inc.</t>
+  </si>
+  <si>
+    <t>2155 University Ave, Bronx, NY 10453, USA</t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
     <t>Spec</t>
   </si>
   <si>
@@ -53,55 +90,85 @@
     <t>Unit</t>
   </si>
   <si>
-    <t>Company</t>
-  </si>
-  <si>
-    <t>Is End User</t>
-  </si>
-  <si>
-    <t>Sell From</t>
-  </si>
-  <si>
-    <t>Yard Address</t>
-  </si>
-  <si>
-    <t>Anson Ni</t>
-  </si>
-  <si>
-    <t>DDP</t>
-  </si>
-  <si>
-    <t>CAD</t>
-  </si>
-  <si>
-    <t>Edmonton</t>
-  </si>
-  <si>
-    <t>API5L 46th Edition B PSL 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPS 1/8 STD </t>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>End</t>
+  </si>
+  <si>
+    <t>Make</t>
+  </si>
+  <si>
+    <t>Hengyang</t>
+  </si>
+  <si>
+    <t>CSAZ245.1:2022 359 Cat II|ASTM/ASME106-19 B</t>
+  </si>
+  <si>
+    <t>NPS 1/2 XXS</t>
   </si>
   <si>
     <t>ft</t>
   </si>
   <si>
-    <t>Precise Pipe</t>
-  </si>
-  <si>
-    <t>Precise Pipe Inc.</t>
-  </si>
-  <si>
-    <t>2155 University Ave, Bronx, NY 10453, USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NPS 1/8 XS </t>
-  </si>
-  <si>
-    <t>ASMESA672 D80</t>
-  </si>
-  <si>
-    <t>NPS 2 1/2 XS</t>
+    <t>SRL</t>
+  </si>
+  <si>
+    <t>Plain End Square Cut</t>
+  </si>
+  <si>
+    <t>Seamless</t>
+  </si>
+  <si>
+    <t>NPS 3/4 XS</t>
+  </si>
+  <si>
+    <t>NPS 1 1/2 S160</t>
+  </si>
+  <si>
+    <t>NPS 1 1/2 STD</t>
+  </si>
+  <si>
+    <t>MSL</t>
+  </si>
+  <si>
+    <t>CSAZ245.1:2022 290 Cat I|ASTM/ASME106-19 B</t>
+  </si>
+  <si>
+    <t>NPS 2 STD</t>
+  </si>
+  <si>
+    <t>DRL</t>
+  </si>
+  <si>
+    <t>Beveled</t>
+  </si>
+  <si>
+    <t>NPS 3 S160</t>
+  </si>
+  <si>
+    <t>NPS 3 STD</t>
+  </si>
+  <si>
+    <t>NPS 4 STD</t>
+  </si>
+  <si>
+    <t>NPS 6 S120</t>
+  </si>
+  <si>
+    <t>NPS 10 STD</t>
+  </si>
+  <si>
+    <t>NPS 10 XS</t>
+  </si>
+  <si>
+    <t>NPS 12 STD</t>
+  </si>
+  <si>
+    <t>NPS 12 XS</t>
+  </si>
+  <si>
+    <t>NPS 16 S80</t>
   </si>
 </sst>
 </file>
@@ -114,25 +181,20 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF161D1D"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF161D1D"/>
-      <name val="Courier New"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -279,18 +341,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -587,70 +643,71 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -665,95 +722,75 @@
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -806,221 +843,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1030,9 +853,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1040,39 +863,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1142,267 +965,739 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="15.75" customWidth="1"/>
-    <col min="4" max="4" width="15.375" customWidth="1"/>
-    <col min="5" max="5" width="32.375" customWidth="1"/>
-    <col min="6" max="6" width="34.25" customWidth="1"/>
-    <col min="9" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="17.875" customWidth="1"/>
-    <col min="12" max="12" width="44.125" customWidth="1"/>
+    <col min="1" max="1" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="13.375" customWidth="1"/>
+    <col min="6" max="6" width="13.375" customWidth="1"/>
+    <col min="7" max="7" width="18.5" customWidth="1"/>
+    <col min="8" max="8" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="D2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
+      <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="H2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="3">
-        <v>100</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" spans="1:12">
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="3">
-        <v>200</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="E4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="3">
-        <v>300</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="E5" s="5"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:H5" numberStoredAsText="1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3">
+        <v>4000</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4">
+        <v>1000</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5">
+        <v>2000</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6">
+        <v>10000</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7">
+        <v>1000</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8">
+        <v>15000</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9">
+        <v>4000</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10">
+        <v>2000</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11">
+        <v>6000</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12">
+        <v>600</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13">
+        <v>8000</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14">
+        <v>3000</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15">
+        <v>1000</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16">
+        <v>600</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17">
+        <v>400</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" t="s">
+        <v>37</v>
+      </c>
+      <c r="H17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:H17" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/demo2.xlsx
+++ b/demo2.xlsx
@@ -496,25 +496,25 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>MSL</v>
+        <v>Hengyang</v>
       </c>
       <c r="B2" t="str">
-        <v>ASTM/ASME333-24 6</v>
+        <v>ASMEB36.10-22|ASTM/ASME106-19 B</v>
       </c>
       <c r="C2" t="str">
-        <v>NPS 16 S120</v>
-      </c>
-      <c r="D2" t="str">
-        <v>96</v>
+        <v>NPS 24 STD</v>
+      </c>
+      <c r="D2">
+        <v>3937</v>
       </c>
       <c r="E2" t="str">
-        <v>m</v>
+        <v>ft</v>
       </c>
       <c r="F2" t="str">
         <v>DRL</v>
       </c>
       <c r="G2" t="str">
-        <v>Plain End Square Cut</v>
+        <v>Beveled</v>
       </c>
       <c r="H2" t="str">
         <v>Seamless</v>
@@ -522,28 +522,28 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>MSL</v>
+        <v>Baosteel</v>
       </c>
       <c r="B3" t="str">
-        <v>ASTM/ASME333-24 6</v>
+        <v>ASMEB36.10-22|API5L 46th Edition B PSL 2</v>
       </c>
       <c r="C3" t="str">
-        <v>NPS 16 S160</v>
-      </c>
-      <c r="D3" t="str">
-        <v>96</v>
+        <v>NPS 24 STD</v>
+      </c>
+      <c r="D3">
+        <v>3937</v>
       </c>
       <c r="E3" t="str">
-        <v>m</v>
+        <v>ft</v>
       </c>
       <c r="F3" t="str">
-        <v>DRL</v>
+        <v>Fixed</v>
       </c>
       <c r="G3" t="str">
-        <v>Plain End Square Cut</v>
+        <v>Beveled</v>
       </c>
       <c r="H3" t="str">
-        <v>Seamless</v>
+        <v>ERW</v>
       </c>
     </row>
   </sheetData>

--- a/demo2.xlsx
+++ b/demo2.xlsx
@@ -466,7 +466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:K7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -493,62 +493,229 @@
       <c r="H1" t="str">
         <v>Make</v>
       </c>
+      <c r="I1" t="str">
+        <v>Min Length</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Max Length</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Fixed Length</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Hengyang</v>
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>ASMEB36.10-22|ASTM/ASME106-19 B</v>
+        <v>API5L 46th Edition X52 PSL 2</v>
       </c>
       <c r="C2" t="str">
-        <v>NPS 24 STD</v>
-      </c>
-      <c r="D2">
-        <v>3937</v>
+        <v>NPS 34 STD</v>
+      </c>
+      <c r="D2" t="str">
+        <v>710</v>
       </c>
       <c r="E2" t="str">
-        <v>ft</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>DRL</v>
+        <v>Fixed</v>
       </c>
       <c r="G2" t="str">
-        <v>Beveled</v>
+        <v>Plain End Square Cut</v>
       </c>
       <c r="H2" t="str">
-        <v>Seamless</v>
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>60</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Baosteel</v>
+        <v/>
       </c>
       <c r="B3" t="str">
-        <v>ASMEB36.10-22|API5L 46th Edition B PSL 2</v>
+        <v>API5L 46th Edition X52 PSL 2</v>
       </c>
       <c r="C3" t="str">
-        <v>NPS 24 STD</v>
-      </c>
-      <c r="D3">
-        <v>3937</v>
+        <v>NPS 34 STD</v>
+      </c>
+      <c r="D3" t="str">
+        <v>710</v>
       </c>
       <c r="E3" t="str">
-        <v>ft</v>
+        <v/>
       </c>
       <c r="F3" t="str">
         <v>Fixed</v>
       </c>
       <c r="G3" t="str">
-        <v>Beveled</v>
+        <v>Plain End Square Cut</v>
       </c>
       <c r="H3" t="str">
-        <v>ERW</v>
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v>API5L 46th Edition X52 PSL 2</v>
+      </c>
+      <c r="C4" t="str">
+        <v>NPS 34 STD</v>
+      </c>
+      <c r="D4" t="str">
+        <v>710</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Plain End Square Cut</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v>API5L 46th Edition X52 PSL 2</v>
+      </c>
+      <c r="C5" t="str">
+        <v>NPS 34 XS</v>
+      </c>
+      <c r="D5" t="str">
+        <v>710</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Plain End Square Cut</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v/>
+      </c>
+      <c r="B6" t="str">
+        <v>API5L 46th Edition X52 PSL 2</v>
+      </c>
+      <c r="C6" t="str">
+        <v>NPS 34 XS</v>
+      </c>
+      <c r="D6" t="str">
+        <v>710</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Plain End Square Cut</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v/>
+      </c>
+      <c r="B7" t="str">
+        <v>API5L 46th Edition X52 PSL 2</v>
+      </c>
+      <c r="C7" t="str">
+        <v>NPS 34 XS</v>
+      </c>
+      <c r="D7" t="str">
+        <v>710</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Plain End Square Cut</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/demo2.xlsx
+++ b/demo2.xlsx
@@ -466,7 +466,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:H3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -493,229 +493,62 @@
       <c r="H1" t="str">
         <v>Make</v>
       </c>
-      <c r="I1" t="str">
-        <v>Min Length</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Max Length</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Fixed Length</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>Hengyang</v>
       </c>
       <c r="B2" t="str">
-        <v>API5L 46th Edition X52 PSL 2</v>
+        <v>API5L 46th Edition B PSL 2</v>
       </c>
       <c r="C2" t="str">
-        <v>NPS 34 STD</v>
+        <v>NPS 24 STD</v>
       </c>
       <c r="D2" t="str">
-        <v>710</v>
+        <v>1200</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>m</v>
       </c>
       <c r="F2" t="str">
-        <v>Fixed</v>
+        <v>DRL</v>
       </c>
       <c r="G2" t="str">
-        <v>Plain End Square Cut</v>
+        <v>Beveled</v>
       </c>
       <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v>60</v>
+        <v>Seamless</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
+        <v>Baosteel</v>
       </c>
       <c r="B3" t="str">
-        <v>API5L 46th Edition X52 PSL 2</v>
+        <v>API5L 46th Edition B PSL 2</v>
       </c>
       <c r="C3" t="str">
-        <v>NPS 34 STD</v>
+        <v>NPS 24 STD</v>
       </c>
       <c r="D3" t="str">
-        <v>710</v>
+        <v>1200</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>m</v>
       </c>
       <c r="F3" t="str">
         <v>Fixed</v>
       </c>
       <c r="G3" t="str">
-        <v>Plain End Square Cut</v>
+        <v>Beveled</v>
       </c>
       <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v/>
-      </c>
-      <c r="B4" t="str">
-        <v>API5L 46th Edition X52 PSL 2</v>
-      </c>
-      <c r="C4" t="str">
-        <v>NPS 34 STD</v>
-      </c>
-      <c r="D4" t="str">
-        <v>710</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Plain End Square Cut</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v/>
-      </c>
-      <c r="B5" t="str">
-        <v>API5L 46th Edition X52 PSL 2</v>
-      </c>
-      <c r="C5" t="str">
-        <v>NPS 34 XS</v>
-      </c>
-      <c r="D5" t="str">
-        <v>710</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Plain End Square Cut</v>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v/>
-      </c>
-      <c r="B6" t="str">
-        <v>API5L 46th Edition X52 PSL 2</v>
-      </c>
-      <c r="C6" t="str">
-        <v>NPS 34 XS</v>
-      </c>
-      <c r="D6" t="str">
-        <v>710</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Plain End Square Cut</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
-      <c r="B7" t="str">
-        <v>API5L 46th Edition X52 PSL 2</v>
-      </c>
-      <c r="C7" t="str">
-        <v>NPS 34 XS</v>
-      </c>
-      <c r="D7" t="str">
-        <v>710</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Plain End Square Cut</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v>20</v>
+        <v>Welded</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>